--- a/artfynd/A 59033-2024 artfynd.xlsx
+++ b/artfynd/A 59033-2024 artfynd.xlsx
@@ -1098,7 +1098,7 @@
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG5" t="b">
         <v>0</v>

--- a/artfynd/A 59033-2024 artfynd.xlsx
+++ b/artfynd/A 59033-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AY49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115891617</v>
+        <v>115891665</v>
       </c>
       <c r="B2" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533089</v>
+        <v>533179</v>
       </c>
       <c r="R2" t="n">
-        <v>7234963</v>
+        <v>7234891</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -762,13 +754,12 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>5760</t>
+          <t>5772</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -790,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115891652</v>
+        <v>115891630</v>
       </c>
       <c r="B3" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -830,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533123</v>
+        <v>533010</v>
       </c>
       <c r="R3" t="n">
-        <v>7234911</v>
+        <v>7234941</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,7 +865,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>5746</t>
+          <t>5753</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -890,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Frida Nettelbladt</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -901,53 +887,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115891627</v>
+        <v>115891647</v>
       </c>
       <c r="B4" t="n">
-        <v>79587</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533098</v>
+        <v>533113</v>
       </c>
       <c r="R4" t="n">
-        <v>7234943</v>
+        <v>7234916</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -988,13 +966,12 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>5765</t>
+          <t>5745</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1005,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Frida Nettelbladt</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1016,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115891679</v>
+        <v>115891739</v>
       </c>
       <c r="B5" t="n">
-        <v>74645</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92721</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6486</v>
+        <v>918</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532889</v>
+        <v>533167</v>
       </c>
       <c r="R5" t="n">
-        <v>7234865</v>
+        <v>7234804</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1098,14 +1070,14 @@
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>5730</t>
+          <t>5747</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1127,15 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115891647</v>
+        <v>115891709</v>
       </c>
       <c r="B6" t="n">
-        <v>78589</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>864</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>533113</v>
+        <v>532923</v>
       </c>
       <c r="R6" t="n">
-        <v>7234916</v>
+        <v>7234841</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1216,7 +1183,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>5745</t>
+          <t>5734</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1238,15 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115891730</v>
+        <v>115891717</v>
       </c>
       <c r="B7" t="n">
-        <v>90346</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1254,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1278,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>533142</v>
+        <v>533162</v>
       </c>
       <c r="R7" t="n">
-        <v>7234812</v>
+        <v>7234838</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1327,7 +1289,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>5751</t>
+          <t>5750</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1349,37 +1311,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115891636</v>
+        <v>115891730</v>
       </c>
       <c r="B8" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1389,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>533093</v>
+        <v>533142</v>
       </c>
       <c r="R8" t="n">
-        <v>7234933</v>
+        <v>7234812</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1438,7 +1395,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>5766</t>
+          <t>5751</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1449,7 +1406,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Frida Nettelbladt</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1460,37 +1417,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115891739</v>
+        <v>115891664</v>
       </c>
       <c r="B9" t="n">
-        <v>91108</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>918</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1500,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>533167</v>
+        <v>533103</v>
       </c>
       <c r="R9" t="n">
-        <v>7234804</v>
+        <v>7234892</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1549,7 +1501,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>5747</t>
+          <t>5744</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1571,37 +1523,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>115891681</v>
+        <v>115891680</v>
       </c>
       <c r="B10" t="n">
-        <v>97671</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>1467</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1558,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>533170</v>
+        <v>532888</v>
       </c>
       <c r="R10" t="n">
-        <v>7234864</v>
+        <v>7234865</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1660,7 +1607,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>5773</t>
+          <t>5736</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1671,7 +1618,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Frida Nettelbladt</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1682,37 +1629,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>115891630</v>
+        <v>115891686</v>
       </c>
       <c r="B11" t="n">
-        <v>78589</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92283</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>864</v>
+        <v>2063</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1722,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>533010</v>
+        <v>533172</v>
       </c>
       <c r="R11" t="n">
-        <v>7234941</v>
+        <v>7234859</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1771,7 +1713,7 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>5753</t>
+          <t>5749</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1782,7 +1724,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Frida Nettelbladt</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1796,12 +1738,7 @@
         <v>115891590</v>
       </c>
       <c r="B12" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,50 +1841,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115891715</v>
+        <v>115891617</v>
       </c>
       <c r="B13" t="n">
-        <v>78758</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6459</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>532895</v>
+        <v>533089</v>
       </c>
       <c r="R13" t="n">
-        <v>7234840</v>
+        <v>7234963</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1988,12 +1923,13 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>5699</t>
+          <t>5760</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2004,7 +1940,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Frida Nettelbladt</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2015,55 +1951,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>115891631</v>
+        <v>115891620</v>
       </c>
       <c r="B14" t="n">
-        <v>5165</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>533010</v>
+        <v>533035</v>
       </c>
       <c r="R14" t="n">
-        <v>7234941</v>
+        <v>7234957</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2107,9 +2033,24 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>fjällbjörk</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Betula pubescens subsp. czerepanovii</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Betula pubescens subsp. czerepanovii</t>
+        </is>
+      </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>5752</t>
+          <t>5757</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2131,15 +2072,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>115891752</v>
+        <v>115891622</v>
       </c>
       <c r="B15" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2171,10 +2107,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>532980</v>
+        <v>533040</v>
       </c>
       <c r="R15" t="n">
-        <v>7234786</v>
+        <v>7234956</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2218,9 +2154,24 @@
       <c r="AG15" t="b">
         <v>0</v>
       </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>fjällbjörk</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Betula pubescens subsp. czerepanovii</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Betula pubescens subsp. czerepanovii</t>
+        </is>
+      </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>5741</t>
+          <t>5755</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2231,7 +2182,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Frida Nettelbladt</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2242,50 +2193,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>115891701</v>
+        <v>115891632</v>
       </c>
       <c r="B16" t="n">
-        <v>79593</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>532903</v>
+        <v>533128</v>
       </c>
       <c r="R16" t="n">
-        <v>7234845</v>
+        <v>7234939</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2326,12 +2275,13 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>5708</t>
+          <t>5769</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2342,7 +2292,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Frida Nettelbladt</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2353,15 +2303,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>115891680</v>
+        <v>115891636</v>
       </c>
       <c r="B17" t="n">
-        <v>74652</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2369,21 +2314,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1467</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2393,10 +2338,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>532888</v>
+        <v>533093</v>
       </c>
       <c r="R17" t="n">
-        <v>7234865</v>
+        <v>7234933</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2442,7 +2387,7 @@
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>5736</t>
+          <t>5766</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2453,7 +2398,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Frida Nettelbladt</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2464,15 +2409,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>115891717</v>
+        <v>115891652</v>
       </c>
       <c r="B18" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2480,21 +2420,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2504,10 +2444,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>533162</v>
+        <v>533123</v>
       </c>
       <c r="R18" t="n">
-        <v>7234838</v>
+        <v>7234911</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2553,7 +2493,7 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>5750</t>
+          <t>5746</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2575,37 +2515,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>115891613</v>
+        <v>115891654</v>
       </c>
       <c r="B19" t="n">
-        <v>79587</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2615,10 +2550,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>533049</v>
+        <v>533123</v>
       </c>
       <c r="R19" t="n">
-        <v>7234967</v>
+        <v>7234908</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2662,24 +2597,9 @@
       <c r="AG19" t="b">
         <v>0</v>
       </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>fjällbjörk</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Betula pubescens subsp. czerepanovii</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Betula pubescens subsp. czerepanovii</t>
-        </is>
-      </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>5759</t>
+          <t>5782</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2701,37 +2621,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>115891686</v>
+        <v>115891698</v>
       </c>
       <c r="B20" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2063</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2741,10 +2656,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>533172</v>
+        <v>532903</v>
       </c>
       <c r="R20" t="n">
-        <v>7234859</v>
+        <v>7234846</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2790,7 +2705,7 @@
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>5749</t>
+          <t>5698</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2812,15 +2727,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>115891622</v>
+        <v>115891752</v>
       </c>
       <c r="B21" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2852,10 +2762,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>533040</v>
+        <v>532980</v>
       </c>
       <c r="R21" t="n">
-        <v>7234956</v>
+        <v>7234786</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2899,24 +2809,9 @@
       <c r="AG21" t="b">
         <v>0</v>
       </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>fjällbjörk</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Betula pubescens subsp. czerepanovii</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Betula pubescens subsp. czerepanovii</t>
-        </is>
-      </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>5755</t>
+          <t>5741</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2927,7 +2822,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Frida Nettelbladt</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2938,37 +2833,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>115891737</v>
+        <v>115891633</v>
       </c>
       <c r="B22" t="n">
-        <v>79464</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2978,10 +2868,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>532930</v>
+        <v>533034</v>
       </c>
       <c r="R22" t="n">
-        <v>7234807</v>
+        <v>7234939</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3027,7 +2917,7 @@
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>5740</t>
+          <t>5754</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3038,7 +2928,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Frida Nettelbladt</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3049,55 +2939,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>115891703</v>
+        <v>115891729</v>
       </c>
       <c r="B23" t="n">
-        <v>5165</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>533192</v>
+        <v>532892</v>
       </c>
       <c r="R23" t="n">
-        <v>7234844</v>
+        <v>7234815</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3143,7 +3023,7 @@
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>5776</t>
+          <t>5697</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3154,7 +3034,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Frida Nettelbladt</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3165,15 +3045,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>115891664</v>
+        <v>115891668</v>
       </c>
       <c r="B24" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3181,21 +3056,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3205,10 +3080,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>533103</v>
+        <v>533161</v>
       </c>
       <c r="R24" t="n">
-        <v>7234892</v>
+        <v>7234890</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3254,7 +3129,7 @@
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>5744</t>
+          <t>5748</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3276,50 +3151,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>115891620</v>
+        <v>115891685</v>
       </c>
       <c r="B25" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>533035</v>
+        <v>533210</v>
       </c>
       <c r="R25" t="n">
-        <v>7234957</v>
+        <v>7234859</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3360,27 +3233,13 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>fjällbjörk</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Betula pubescens subsp. czerepanovii</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Betula pubescens subsp. czerepanovii</t>
-        </is>
-      </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>5757</t>
+          <t>5777</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3402,15 +3261,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>115891628</v>
+        <v>115891737</v>
       </c>
       <c r="B26" t="n">
-        <v>79594</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3418,37 +3272,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6464</v>
+        <v>6456</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>533098</v>
+        <v>532930</v>
       </c>
       <c r="R26" t="n">
-        <v>7234943</v>
+        <v>7234807</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3489,13 +3340,12 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>5763</t>
+          <t>5740</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3506,7 +3356,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Frida Nettelbladt</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3517,37 +3367,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>115891637</v>
+        <v>115891591</v>
       </c>
       <c r="B27" t="n">
-        <v>79594</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3557,10 +3402,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>533093</v>
+        <v>533163</v>
       </c>
       <c r="R27" t="n">
-        <v>7234933</v>
+        <v>7235002</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3606,7 +3451,7 @@
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>5767</t>
+          <t>5778</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3628,50 +3473,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>115891698</v>
+        <v>115891618</v>
       </c>
       <c r="B28" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79583</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>6459</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>532903</v>
+        <v>533089</v>
       </c>
       <c r="R28" t="n">
-        <v>7234846</v>
+        <v>7234963</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3712,12 +3555,13 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>5698</t>
+          <t>5761</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3728,7 +3572,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Frida Nettelbladt</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3739,37 +3583,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>115891665</v>
+        <v>115891715</v>
       </c>
       <c r="B29" t="n">
-        <v>86661</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79583</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>510</v>
+        <v>6459</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3779,10 +3618,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>533179</v>
+        <v>532895</v>
       </c>
       <c r="R29" t="n">
-        <v>7234891</v>
+        <v>7234840</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3828,7 +3667,7 @@
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>5772</t>
+          <t>5699</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3839,7 +3678,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Frida Nettelbladt</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3850,37 +3689,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>115891709</v>
+        <v>115891589</v>
       </c>
       <c r="B30" t="n">
-        <v>90328</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3890,10 +3724,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>532923</v>
+        <v>533163</v>
       </c>
       <c r="R30" t="n">
-        <v>7234841</v>
+        <v>7235002</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3939,7 +3773,7 @@
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>5734</t>
+          <t>5780</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3950,7 +3784,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Frida Nettelbladt</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3961,37 +3795,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>115891614</v>
+        <v>115891613</v>
       </c>
       <c r="B31" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4001,10 +3830,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>533034</v>
+        <v>533049</v>
       </c>
       <c r="R31" t="n">
-        <v>7234965</v>
+        <v>7234967</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4048,9 +3877,24 @@
       <c r="AG31" t="b">
         <v>0</v>
       </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>fjällbjörk</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Betula pubescens subsp. czerepanovii</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Betula pubescens subsp. czerepanovii</t>
+        </is>
+      </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>5758</t>
+          <t>5759</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4072,50 +3916,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>115891668</v>
+        <v>115891627</v>
       </c>
       <c r="B32" t="n">
-        <v>74647</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>533161</v>
+        <v>533098</v>
       </c>
       <c r="R32" t="n">
-        <v>7234890</v>
+        <v>7234943</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4156,12 +3998,13 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>5748</t>
+          <t>5765</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4172,7 +4015,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Frida Nettelbladt</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4183,15 +4026,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>115891696</v>
+        <v>115891695</v>
       </c>
       <c r="B33" t="n">
-        <v>79594</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4199,21 +4037,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4223,10 +4061,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>532898</v>
+        <v>532901</v>
       </c>
       <c r="R33" t="n">
-        <v>7234848</v>
+        <v>7234849</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4272,7 +4110,7 @@
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>5709</t>
+          <t>5711</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4294,37 +4132,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>115891591</v>
+        <v>115891621</v>
       </c>
       <c r="B34" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4334,10 +4167,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>533163</v>
+        <v>533041</v>
       </c>
       <c r="R34" t="n">
-        <v>7235002</v>
+        <v>7234956</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4381,9 +4214,24 @@
       <c r="AG34" t="b">
         <v>0</v>
       </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>fjällbjörk</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Betula pubescens subsp. czerepanovii</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Betula pubescens subsp. czerepanovii</t>
+        </is>
+      </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>5778</t>
+          <t>5756</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4405,32 +4253,27 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>115891633</v>
+        <v>115891629</v>
       </c>
       <c r="B35" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4439,16 +4282,19 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>533034</v>
+        <v>533098</v>
       </c>
       <c r="R35" t="n">
-        <v>7234939</v>
+        <v>7234943</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4489,12 +4335,13 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>5754</t>
+          <t>5764</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4516,37 +4363,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>115891654</v>
+        <v>115891701</v>
       </c>
       <c r="B36" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4556,10 +4398,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>533123</v>
+        <v>532903</v>
       </c>
       <c r="R36" t="n">
-        <v>7234908</v>
+        <v>7234845</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4605,7 +4447,7 @@
       </c>
       <c r="AR36" t="inlineStr">
         <is>
-          <t>5782</t>
+          <t>5708</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4616,7 +4458,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Frida Nettelbladt</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4627,15 +4469,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>115891645</v>
+        <v>115891628</v>
       </c>
       <c r="B37" t="n">
-        <v>96616</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4643,34 +4480,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221941</v>
+        <v>6464</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>533079</v>
+        <v>533098</v>
       </c>
       <c r="R37" t="n">
-        <v>7234917</v>
+        <v>7234943</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4711,12 +4551,13 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AR37" t="inlineStr">
         <is>
-          <t>5781</t>
+          <t>5763</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4738,55 +4579,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>115891623</v>
+        <v>115891637</v>
       </c>
       <c r="B38" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>533103</v>
+        <v>533093</v>
       </c>
       <c r="R38" t="n">
-        <v>7234953</v>
+        <v>7234933</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4821,11 +4652,6 @@
           <t>2023-06-16</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>färska hackspår (ringhack på gran)</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4837,7 +4663,7 @@
       </c>
       <c r="AR38" t="inlineStr">
         <is>
-          <t>5762</t>
+          <t>5767</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4859,37 +4685,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>115891729</v>
+        <v>115891696</v>
       </c>
       <c r="B39" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4899,10 +4720,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>532892</v>
+        <v>532898</v>
       </c>
       <c r="R39" t="n">
-        <v>7234815</v>
+        <v>7234848</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4948,7 +4769,7 @@
       </c>
       <c r="AR39" t="inlineStr">
         <is>
-          <t>5697</t>
+          <t>5709</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4970,53 +4791,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>115891629</v>
+        <v>115891679</v>
       </c>
       <c r="B40" t="n">
-        <v>79593</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83305</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6463</v>
+        <v>6486</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>533098</v>
+        <v>532889</v>
       </c>
       <c r="R40" t="n">
-        <v>7234943</v>
+        <v>7234865</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5055,15 +4868,14 @@
         <v>0</v>
       </c>
       <c r="AE40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF40" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AR40" t="inlineStr">
         <is>
-          <t>5764</t>
+          <t>5730</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5074,7 +4886,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Frida Nettelbladt</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -5085,50 +4897,50 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>115891621</v>
+        <v>115891623</v>
       </c>
       <c r="B41" t="n">
-        <v>79593</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>533041</v>
+        <v>533103</v>
       </c>
       <c r="R41" t="n">
-        <v>7234956</v>
+        <v>7234953</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5163,6 +4975,11 @@
           <t>2023-06-16</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>färska hackspår (ringhack på gran)</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5172,24 +4989,9 @@
       <c r="AG41" t="b">
         <v>0</v>
       </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>fjällbjörk</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Betula pubescens subsp. czerepanovii</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Betula pubescens subsp. czerepanovii</t>
-        </is>
-      </c>
       <c r="AR41" t="inlineStr">
         <is>
-          <t>5756</t>
+          <t>5762</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5211,53 +5013,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>115891632</v>
+        <v>115891631</v>
       </c>
       <c r="B42" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>100526</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>533128</v>
+        <v>533010</v>
       </c>
       <c r="R42" t="n">
-        <v>7234939</v>
+        <v>7234941</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5298,13 +5097,12 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AR42" t="inlineStr">
         <is>
-          <t>5769</t>
+          <t>5752</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5326,15 +5124,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>115891719</v>
+        <v>115891703</v>
       </c>
       <c r="B43" t="n">
-        <v>97671</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5342,34 +5135,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221952</v>
+        <v>100526</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>533171</v>
+        <v>533192</v>
       </c>
       <c r="R43" t="n">
-        <v>7234837</v>
+        <v>7234844</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5415,7 +5213,7 @@
       </c>
       <c r="AR43" t="inlineStr">
         <is>
-          <t>5775</t>
+          <t>5776</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5437,37 +5235,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>115891704</v>
+        <v>115891738</v>
       </c>
       <c r="B44" t="n">
-        <v>79518</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229497</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5477,10 +5270,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>532900</v>
+        <v>532774</v>
       </c>
       <c r="R44" t="n">
-        <v>7234844</v>
+        <v>7234807</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5507,12 +5300,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2023-06-16</t>
+          <t>2023-09-15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2023-06-16</t>
+          <t>2023-09-15</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5526,7 +5319,7 @@
       </c>
       <c r="AR44" t="inlineStr">
         <is>
-          <t>5700</t>
+          <t>7448</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5537,7 +5330,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Josefina Pehrson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5548,15 +5341,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>115891618</v>
+        <v>115891645</v>
       </c>
       <c r="B45" t="n">
-        <v>78758</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5564,37 +5352,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6459</v>
+        <v>221941</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>533089</v>
+        <v>533079</v>
       </c>
       <c r="R45" t="n">
-        <v>7234963</v>
+        <v>7234917</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5635,13 +5420,12 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AR45" t="inlineStr">
         <is>
-          <t>5761</t>
+          <t>5781</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5663,15 +5447,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>115891589</v>
+        <v>115891681</v>
       </c>
       <c r="B46" t="n">
-        <v>79587</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5679,21 +5458,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5703,10 +5482,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>533163</v>
+        <v>533170</v>
       </c>
       <c r="R46" t="n">
-        <v>7235002</v>
+        <v>7234864</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5752,7 +5531,7 @@
       </c>
       <c r="AR46" t="inlineStr">
         <is>
-          <t>5780</t>
+          <t>5773</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5774,37 +5553,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>115891746</v>
+        <v>115891719</v>
       </c>
       <c r="B47" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5814,10 +5588,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>532861</v>
+        <v>533171</v>
       </c>
       <c r="R47" t="n">
-        <v>7234795</v>
+        <v>7234837</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5863,7 +5637,7 @@
       </c>
       <c r="AR47" t="inlineStr">
         <is>
-          <t>5695</t>
+          <t>5775</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5874,7 +5648,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Frida Nettelbladt</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5885,15 +5659,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>115891695</v>
+        <v>115891558</v>
       </c>
       <c r="B48" t="n">
-        <v>79587</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5901,21 +5670,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6462</v>
+        <v>229497</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5925,10 +5694,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>532901</v>
+        <v>533180</v>
       </c>
       <c r="R48" t="n">
-        <v>7234849</v>
+        <v>7235033</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5974,7 +5743,7 @@
       </c>
       <c r="AR48" t="inlineStr">
         <is>
-          <t>5711</t>
+          <t>5783</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5985,10 +5754,116 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Frida Nettelbladt</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
+        <is>
+          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>115891704</v>
+      </c>
+      <c r="B49" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Dikanäs - Kittelfjäll, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>532900</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7234844</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>5700</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Rickard Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Rickard Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
         <is>
           <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
         </is>
